--- a/EndResult/100m Medley.xlsx
+++ b/EndResult/100m Medley.xlsx
@@ -928,20 +928,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.03,84</t>
+          <t>1.02,21</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.11.2024</t>
+          <t>16.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bodø</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/EndResult/100m Medley.xlsx
+++ b/EndResult/100m Medley.xlsx
@@ -646,12 +646,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Albert Barrabino</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.00,69</t>
+          <t>1.00,70</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -659,12 +659,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>28.09.2024</t>
+          <t>25.03.2012</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Drammen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -681,12 +681,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Albert Barrabino</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.00,70</t>
+          <t>1.00,69</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -694,12 +694,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25.03.2012</t>
+          <t>28.09.2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drammen</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -928,20 +928,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.02,21</t>
+          <t>1.03,61</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.11.2025</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1238,12 +1238,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Karoline Volden</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.09,69</t>
+          <t>1.09,68</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.09.2017</t>
+          <t>27.05.2017</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
